--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.8763320360905</v>
+        <v>7.617403955864706</v>
       </c>
       <c r="D2" t="n">
-        <v>47.27622810858423</v>
+        <v>7.682387067644937</v>
       </c>
       <c r="E2" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F2" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.93629112230673</v>
+        <v>6.652147307374845</v>
       </c>
       <c r="D3" t="n">
-        <v>23.39762681960625</v>
+        <v>3.802114358186016</v>
       </c>
       <c r="E3" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F3" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.72274293268884</v>
+        <v>7.104945726561937</v>
       </c>
       <c r="D4" t="n">
-        <v>6.193704633311236</v>
+        <v>1.006477002913076</v>
       </c>
       <c r="E4" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.37255271784871</v>
+        <v>5.260539816650414</v>
       </c>
       <c r="D5" t="n">
-        <v>31.69492550472579</v>
+        <v>5.150425394517942</v>
       </c>
       <c r="E5" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F5" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.60854983246382</v>
+        <v>6.923889347775371</v>
       </c>
       <c r="D6" t="n">
-        <v>7.583828356303018</v>
+        <v>1.23237210789924</v>
       </c>
       <c r="E6" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F6" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.44210041710693</v>
+        <v>6.734341317779876</v>
       </c>
       <c r="D7" t="n">
-        <v>20.54043850136087</v>
+        <v>3.337821256471142</v>
       </c>
       <c r="E7" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F7" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.87326652963073</v>
+        <v>1.929405811064994</v>
       </c>
       <c r="D8" t="n">
-        <v>12.69887904099684</v>
+        <v>2.063567844161986</v>
       </c>
       <c r="E8" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F8" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.77057879191075</v>
+        <v>5.650219053685497</v>
       </c>
       <c r="D9" t="n">
-        <v>33.73083792211341</v>
+        <v>5.481261162343429</v>
       </c>
       <c r="E9" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F9" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.06988535559694</v>
+        <v>2.611356370284504</v>
       </c>
       <c r="D10" t="n">
-        <v>15.64629239241379</v>
+        <v>2.542522513767241</v>
       </c>
       <c r="E10" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F10" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.33820587757636</v>
+        <v>5.417458455106158</v>
       </c>
       <c r="D11" t="n">
-        <v>30.91230113868636</v>
+        <v>5.023248935036533</v>
       </c>
       <c r="E11" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F11" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.76851874981018</v>
+        <v>5.812384296844154</v>
       </c>
       <c r="D12" t="n">
-        <v>35.81335486777573</v>
+        <v>5.819670166013556</v>
       </c>
       <c r="E12" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F12" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.82514204206307</v>
+        <v>6.959085581835249</v>
       </c>
       <c r="D13" t="n">
-        <v>42.29293990885424</v>
+        <v>6.872602735188813</v>
       </c>
       <c r="E13" t="n">
-        <v>10.47192592453993</v>
+        <v>1.701687962737739</v>
       </c>
       <c r="F13" t="n">
-        <v>12.84986483156992</v>
+        <v>2.088103035130112</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
